--- a/ig/DM-DECEMBRE-2025/ValueSet-JDV-J148-ReferenceRangeAppliesTo-CISIS.xlsx
+++ b/ig/DM-DECEMBRE-2025/ValueSet-JDV-J148-ReferenceRangeAppliesTo-CISIS.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="37">
   <si>
     <t>Property</t>
   </si>
@@ -122,9 +122,6 @@
   </si>
   <si>
     <t>77386006</t>
-  </si>
-  <si>
-    <t>enceinte</t>
   </si>
   <si>
     <t>http://snomed.info/sct</t>
@@ -462,9 +459,7 @@
       <c r="A2" t="s" s="2">
         <v>35</v>
       </c>
-      <c r="B2" t="s" s="2">
-        <v>36</v>
-      </c>
+      <c r="B2" s="2"/>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
@@ -479,7 +474,7 @@
         <v>33</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
   </sheetData>
